--- a/blocks_conditions.xlsx
+++ b/blocks_conditions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryantracy/Desktop/andre rc studies/police meta perceptions project/study 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{591EE16C-F083-2B44-99A0-41F3728042E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F5F234-4898-624A-BB35-BFA153068F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{2DF570FD-F668-2042-AAE4-9922E675E617}"/>
   </bookViews>
@@ -36,15 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>block_name</t>
-  </si>
-  <si>
-    <t>police_fight_flight_set</t>
-  </si>
-  <si>
-    <t>police_avoidance_set</t>
   </si>
   <si>
     <t>gblems_set</t>
@@ -425,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BAB583-5CB7-264D-B508-FFF66B700D4F}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -448,16 +442,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/blocks_conditions.xlsx
+++ b/blocks_conditions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryantracy/Desktop/andre rc studies/police meta perceptions project/study 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F5F234-4898-624A-BB35-BFA153068F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D15C20-1AF5-5D4C-9C81-F2C6FE330A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{2DF570FD-F668-2042-AAE4-9922E675E617}"/>
   </bookViews>
@@ -44,10 +44,10 @@
     <t>gblems_set</t>
   </si>
   <si>
-    <t>gblems_expanded_set</t>
+    <t>group_mem_set</t>
   </si>
   <si>
-    <t>group_mem_set</t>
+    <t>police_avoidance</t>
   </si>
 </sst>
 </file>
@@ -434,12 +434,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
